--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -18925,7 +18925,7 @@
     <t>review_wrong_words</t>
   </si>
   <si>
-    <t>复习错词</t>
+    <t>错词巩固</t>
   </si>
   <si>
     <t>Review Wrong Words</t>
@@ -32783,6 +32783,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32797,6 +32803,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32814,6 +32826,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32831,6 +32849,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32848,6 +32872,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32865,6 +32895,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32882,6 +32918,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32899,6 +32941,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32916,6 +32964,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -32933,6 +32987,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>播放例句</t>
     </r>
     <r>
@@ -72017,7 +72077,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A245:O245 D246:O246 A247:O254 A256:O509 A1:O243 A535:A546 A549:A776" numberStoredAsText="1"/>
+    <ignoredError sqref="A549:A776 A535:A546 A1:O243 A256:O450 A451 C451:O451 A452:O509 A247:O254 D246:O246 A245:O245" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>